--- a/hanzicraft_dashboard.xlsx
+++ b/hanzicraft_dashboard.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:C251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,11 @@
           <t>Chữ Hán</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -437,6 +442,11 @@
           <t>的</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9A%84</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -447,6 +457,11 @@
           <t>一</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%80</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -457,6 +472,11 @@
           <t>是</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%AF</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -467,6 +487,11 @@
           <t>不</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%8D</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -477,6 +502,11 @@
           <t>了</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%86</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -487,6 +517,11 @@
           <t>在</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9C%A8</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -497,6 +532,11 @@
           <t>人</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%BA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -507,6 +547,11 @@
           <t>有</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%89</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -517,6 +562,11 @@
           <t>我</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%91</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -527,6 +577,11 @@
           <t>他</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%96</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -537,6 +592,11 @@
           <t>这</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -547,6 +607,11 @@
           <t>个</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%AA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -557,6 +622,11 @@
           <t>们</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%AC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -567,6 +637,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%AD</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -577,6 +652,11 @@
           <t>来</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9D%A5</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -587,6 +667,11 @@
           <t>上</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%8A</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -597,6 +682,11 @@
           <t>大</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%A7</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -607,6 +697,11 @@
           <t>为</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%BA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -617,6 +712,11 @@
           <t>和</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%92%8C</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -627,6 +727,11 @@
           <t>国</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9B%BD</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +742,11 @@
           <t>地</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9C%B0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -647,6 +757,11 @@
           <t>到</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%B0</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -657,6 +772,11 @@
           <t>以</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%A5</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -667,6 +787,11 @@
           <t>说</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%B4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -677,6 +802,11 @@
           <t>时</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%97%B6</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -687,6 +817,11 @@
           <t>要</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A6%81</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -697,6 +832,11 @@
           <t>就</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%B1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -707,6 +847,11 @@
           <t>出</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%BA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -717,6 +862,11 @@
           <t>会</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BC%9A</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -727,6 +877,11 @@
           <t>可</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%AF</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -737,6 +892,11 @@
           <t>也</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%9F</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -747,6 +907,11 @@
           <t>你</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%A0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -757,6 +922,11 @@
           <t>对</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%B9</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -767,6 +937,11 @@
           <t>生</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%94%9F</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -777,6 +952,11 @@
           <t>能</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%83%BD</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -787,6 +967,11 @@
           <t>而</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%8C</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -797,6 +982,11 @@
           <t>子</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AD%90</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -807,6 +997,11 @@
           <t>那</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%82%A3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -817,6 +1012,11 @@
           <t>得</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BE%97</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -827,6 +1027,11 @@
           <t>于</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%8E</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -837,6 +1042,11 @@
           <t>着</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9D%80</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -847,6 +1057,11 @@
           <t>下</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%8B</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -857,6 +1072,11 @@
           <t>自</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%87%AA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -867,6 +1087,11 @@
           <t>之</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%8B</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -877,6 +1102,11 @@
           <t>年</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%B4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -887,6 +1117,11 @@
           <t>过</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%87</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -897,6 +1132,11 @@
           <t>发</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%91</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -907,6 +1147,11 @@
           <t>后</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%8E</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -917,6 +1162,11 @@
           <t>作</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%9C</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -927,6 +1177,11 @@
           <t>里</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%87%8C</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -937,6 +1192,11 @@
           <t>用</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%94%A8</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -947,6 +1207,11 @@
           <t>道</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%81%93</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -957,6 +1222,11 @@
           <t>行</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A1%8C</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -967,6 +1237,11 @@
           <t>所</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%80</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -977,6 +1252,11 @@
           <t>然</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%84%B6</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -987,6 +1267,11 @@
           <t>家</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%B6</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -997,6 +1282,11 @@
           <t>种</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A7%8D</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1007,6 +1297,11 @@
           <t>事</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%8B</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1017,6 +1312,11 @@
           <t>成</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%90</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1027,6 +1327,11 @@
           <t>方</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%B9</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1037,6 +1342,11 @@
           <t>多</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%9A</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1047,6 +1357,11 @@
           <t>经</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%8F</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1057,6 +1372,11 @@
           <t>么</t>
         </is>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%88</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1067,6 +1387,11 @@
           <t>去</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8E%BB</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1077,6 +1402,11 @@
           <t>法</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B3%95</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1087,6 +1417,11 @@
           <t>学</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AD%A6</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1097,6 +1432,11 @@
           <t>如</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A6%82</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1107,6 +1447,11 @@
           <t>都</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%83%BD</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1117,6 +1462,11 @@
           <t>同</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%8C</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1127,6 +1477,11 @@
           <t>现</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8E%B0</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1137,6 +1492,11 @@
           <t>当</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BD%93</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1147,6 +1507,11 @@
           <t>没</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B2%A1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1157,6 +1522,11 @@
           <t>动</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%A8</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1167,6 +1537,11 @@
           <t>面</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9D%A2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1177,6 +1552,11 @@
           <t>起</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%B7</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1187,6 +1567,11 @@
           <t>看</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9C%8B</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1197,6 +1582,11 @@
           <t>定</t>
         </is>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%9A</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1207,6 +1597,11 @@
           <t>天</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%A9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1217,6 +1612,11 @@
           <t>分</t>
         </is>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%86</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1227,6 +1627,11 @@
           <t>还</t>
         </is>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%98</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1237,6 +1642,11 @@
           <t>进</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%9B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1247,6 +1657,11 @@
           <t>好</t>
         </is>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%BD</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1257,6 +1672,11 @@
           <t>小</t>
         </is>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%8F</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1267,6 +1687,11 @@
           <t>部</t>
         </is>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%83%A8</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1277,6 +1702,11 @@
           <t>其</t>
         </is>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%B6</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1287,6 +1717,11 @@
           <t>些</t>
         </is>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%9B</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1297,6 +1732,11 @@
           <t>主</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%BB</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1307,6 +1747,11 @@
           <t>样</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A0%B7</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1317,6 +1762,11 @@
           <t>理</t>
         </is>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%90%86</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1327,6 +1777,11 @@
           <t>心</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BF%83</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1337,6 +1792,11 @@
           <t>她</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%B9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1347,6 +1807,11 @@
           <t>本</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%AC</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1357,6 +1822,11 @@
           <t>前</t>
         </is>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%89%8D</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1367,6 +1837,11 @@
           <t>开</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%80</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1377,6 +1852,11 @@
           <t>但</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%86</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1387,6 +1867,11 @@
           <t>因</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9B%A0</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1397,6 +1882,11 @@
           <t>只</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%AA</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1407,6 +1897,11 @@
           <t>从</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%8E</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1417,6 +1912,11 @@
           <t>想</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%B3</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1427,6 +1927,11 @@
           <t>实</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%9E</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1437,6 +1942,11 @@
           <t>日</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%97%A5</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1447,6 +1957,11 @@
           <t>军</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%9B</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1457,6 +1972,11 @@
           <t>者</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%85</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1467,6 +1987,11 @@
           <t>意</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%84%8F</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1477,6 +2002,11 @@
           <t>无</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%97%A0</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1487,6 +2017,11 @@
           <t>力</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%9B</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1497,6 +2032,11 @@
           <t>它</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%83</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1507,6 +2047,11 @@
           <t>与</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%8E</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1517,6 +2062,11 @@
           <t>长</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%95%BF</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1527,6 +2077,11 @@
           <t>把</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%8A</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1537,6 +2092,11 @@
           <t>机</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%BA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -1547,6 +2107,11 @@
           <t>十</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%81</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -1557,6 +2122,11 @@
           <t>民</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B0%91</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -1567,6 +2137,11 @@
           <t>第</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AC%AC</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -1577,6 +2152,11 @@
           <t>公</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%AC</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -1587,6 +2167,11 @@
           <t>此</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AD%A4</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -1597,6 +2182,11 @@
           <t>已</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B7%B2</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -1607,6 +2197,11 @@
           <t>工</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B7%A5</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -1617,6 +2212,11 @@
           <t>使</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%BF</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -1627,6 +2227,11 @@
           <t>情</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%83%85</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -1637,6 +2242,11 @@
           <t>明</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%8E</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -1647,6 +2257,11 @@
           <t>性</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%A7</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -1657,6 +2272,11 @@
           <t>知</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9F%A5</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -1667,6 +2287,11 @@
           <t>全</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%A8</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -1677,6 +2302,11 @@
           <t>三</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%89</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -1687,6 +2317,11 @@
           <t>又</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%88</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -1697,6 +2332,11 @@
           <t>关</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%B3</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -1707,6 +2347,11 @@
           <t>点</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%82%B9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -1717,6 +2362,11 @@
           <t>正</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AD%A3</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -1727,6 +2377,11 @@
           <t>业</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%9A</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -1737,6 +2392,11 @@
           <t>外</t>
         </is>
       </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%96</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -1747,6 +2407,11 @@
           <t>将</t>
         </is>
       </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%86</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -1757,6 +2422,11 @@
           <t>两</t>
         </is>
       </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%A4</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -1767,6 +2437,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%AB%98</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -1777,6 +2452,11 @@
           <t>间</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%97%B4</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -1787,6 +2467,11 @@
           <t>由</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%94%B1</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -1797,6 +2482,11 @@
           <t>问</t>
         </is>
       </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%97%AE</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -1807,6 +2497,11 @@
           <t>很</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BE%88</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -1817,6 +2512,11 @@
           <t>最</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%80</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -1827,6 +2527,11 @@
           <t>重</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%87%8D</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -1837,6 +2542,11 @@
           <t>并</t>
         </is>
       </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%B6</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -1847,6 +2557,11 @@
           <t>物</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%A9</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -1857,6 +2572,11 @@
           <t>手</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%8B</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -1867,6 +2587,11 @@
           <t>应</t>
         </is>
       </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BA%94</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -1877,6 +2602,11 @@
           <t>战</t>
         </is>
       </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%98</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -1887,6 +2617,11 @@
           <t>向</t>
         </is>
       </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%91</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -1897,6 +2632,11 @@
           <t>头</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%B4</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -1907,6 +2647,11 @@
           <t>文</t>
         </is>
       </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%87</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -1917,6 +2662,11 @@
           <t>体</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%93</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -1927,6 +2677,11 @@
           <t>政</t>
         </is>
       </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%94%BF</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -1937,6 +2692,11 @@
           <t>美</t>
         </is>
       </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BE%8E</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -1947,6 +2707,11 @@
           <t>相</t>
         </is>
       </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9B%B8</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -1957,6 +2722,11 @@
           <t>见</t>
         </is>
       </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%81</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -1967,6 +2737,11 @@
           <t>被</t>
         </is>
       </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A2%AB</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -1977,6 +2752,11 @@
           <t>利</t>
         </is>
       </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%A9</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -1987,6 +2767,11 @@
           <t>什</t>
         </is>
       </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%80</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -1997,6 +2782,11 @@
           <t>二</t>
         </is>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%8C</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2007,6 +2797,11 @@
           <t>等</t>
         </is>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AD%89</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2017,6 +2812,11 @@
           <t>产</t>
         </is>
       </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%A7</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2027,6 +2827,11 @@
           <t>或</t>
         </is>
       </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%88%96</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2037,6 +2842,11 @@
           <t>新</t>
         </is>
       </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%B0</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2047,6 +2857,11 @@
           <t>己</t>
         </is>
       </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B7%B1</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2057,6 +2872,11 @@
           <t>制</t>
         </is>
       </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%B6</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2067,6 +2887,11 @@
           <t>身</t>
         </is>
       </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BA%AB</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2077,6 +2902,11 @@
           <t>果</t>
         </is>
       </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9E%9C</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2087,6 +2917,11 @@
           <t>加</t>
         </is>
       </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%A0</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2097,6 +2932,11 @@
           <t>西</t>
         </is>
       </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A5%BF</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2107,6 +2947,11 @@
           <t>斯</t>
         </is>
       </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%AF</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2117,6 +2962,11 @@
           <t>月</t>
         </is>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%88</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2127,6 +2977,11 @@
           <t>话</t>
         </is>
       </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%9D</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2137,6 +2992,11 @@
           <t>合</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%88</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2147,6 +3007,11 @@
           <t>回</t>
         </is>
       </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9B%9E</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2157,6 +3022,11 @@
           <t>特</t>
         </is>
       </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%B9</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2167,6 +3037,11 @@
           <t>代</t>
         </is>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%A3</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2177,6 +3052,11 @@
           <t>内</t>
         </is>
       </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%85</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2187,6 +3067,11 @@
           <t>信</t>
         </is>
       </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BF%A1</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2197,6 +3082,11 @@
           <t>表</t>
         </is>
       </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A1%A8</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2207,6 +3097,11 @@
           <t>化</t>
         </is>
       </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%96</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2217,6 +3112,11 @@
           <t>老</t>
         </is>
       </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%81</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2227,6 +3127,11 @@
           <t>给</t>
         </is>
       </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%99</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2237,6 +3142,11 @@
           <t>世</t>
         </is>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%96</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2247,6 +3157,11 @@
           <t>位</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%8D</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2257,6 +3172,11 @@
           <t>次</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AC%A1</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -2267,6 +3187,11 @@
           <t>度</t>
         </is>
       </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BA%A6</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -2277,6 +3202,11 @@
           <t>门</t>
         </is>
       </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%97%A8</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -2287,6 +3217,11 @@
           <t>任</t>
         </is>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%BB</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -2297,6 +3232,11 @@
           <t>常</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%B8</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -2307,6 +3247,11 @@
           <t>先</t>
         </is>
       </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%88</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -2317,6 +3262,11 @@
           <t>海</t>
         </is>
       </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%B7</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -2327,6 +3277,11 @@
           <t>通</t>
         </is>
       </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%9A</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -2337,6 +3292,11 @@
           <t>教</t>
         </is>
       </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%95%99</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -2347,6 +3307,11 @@
           <t>儿</t>
         </is>
       </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%84%BF</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -2357,6 +3322,11 @@
           <t>原</t>
         </is>
       </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8E%9F</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -2367,6 +3337,11 @@
           <t>东</t>
         </is>
       </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%9C</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -2377,6 +3352,11 @@
           <t>声</t>
         </is>
       </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A3%B0</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -2387,6 +3367,11 @@
           <t>提</t>
         </is>
       </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8F%90</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -2397,6 +3382,11 @@
           <t>立</t>
         </is>
       </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AB%8B</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -2407,6 +3397,11 @@
           <t>及</t>
         </is>
       </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%8A</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -2417,6 +3412,11 @@
           <t>比</t>
         </is>
       </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AF%94</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -2427,6 +3427,11 @@
           <t>员</t>
         </is>
       </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%98</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -2437,6 +3442,11 @@
           <t>解</t>
         </is>
       </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%A3</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -2447,6 +3457,11 @@
           <t>水</t>
         </is>
       </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B0%B4</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -2457,6 +3472,11 @@
           <t>名</t>
         </is>
       </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%8D</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -2467,6 +3487,11 @@
           <t>真</t>
         </is>
       </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9C%9F</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -2477,6 +3502,11 @@
           <t>论</t>
         </is>
       </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%BA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -2487,6 +3517,11 @@
           <t>处</t>
         </is>
       </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%84</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -2497,6 +3532,11 @@
           <t>走</t>
         </is>
       </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%B0</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -2507,6 +3547,11 @@
           <t>义</t>
         </is>
       </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%89</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -2517,6 +3562,11 @@
           <t>各</t>
         </is>
       </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%84</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -2527,6 +3577,11 @@
           <t>入</t>
         </is>
       </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%A5</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -2537,6 +3592,11 @@
           <t>几</t>
         </is>
       </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%A0</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -2547,6 +3607,11 @@
           <t>口</t>
         </is>
       </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%A3</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -2557,6 +3622,11 @@
           <t>认</t>
         </is>
       </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%A4</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -2567,6 +3637,11 @@
           <t>条</t>
         </is>
       </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9D%A1</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -2577,6 +3652,11 @@
           <t>平</t>
         </is>
       </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%B3</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -2587,6 +3667,11 @@
           <t>系</t>
         </is>
       </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B3%BB</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -2597,6 +3682,11 @@
           <t>气</t>
         </is>
       </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B0%94</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -2607,6 +3697,11 @@
           <t>题</t>
         </is>
       </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A2%98</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -2617,6 +3712,11 @@
           <t>活</t>
         </is>
       </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B4%BB</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -2627,6 +3727,11 @@
           <t>尔</t>
         </is>
       </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%94</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -2637,6 +3742,11 @@
           <t>更</t>
         </is>
       </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9B%B4</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -2647,6 +3757,11 @@
           <t>别</t>
         </is>
       </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%AB</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -2657,6 +3772,11 @@
           <t>打</t>
         </is>
       </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%93</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -2667,6 +3787,11 @@
           <t>女</t>
         </is>
       </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A5%B3</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -2677,6 +3802,11 @@
           <t>变</t>
         </is>
       </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%98</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -2687,6 +3817,11 @@
           <t>四</t>
         </is>
       </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9B%9B</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -2697,6 +3832,11 @@
           <t>神</t>
         </is>
       </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A5%9E</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -2707,6 +3847,11 @@
           <t>总</t>
         </is>
       </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%BB</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -2717,6 +3862,11 @@
           <t>何</t>
         </is>
       </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%95</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -2727,6 +3877,11 @@
           <t>电</t>
         </is>
       </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%94%B5</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -2737,6 +3892,11 @@
           <t>数</t>
         </is>
       </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%95%B0</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -2747,6 +3907,11 @@
           <t>安</t>
         </is>
       </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%89</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -2757,6 +3922,11 @@
           <t>少</t>
         </is>
       </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%91</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -2767,6 +3937,11 @@
           <t>报</t>
         </is>
       </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%A5</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -2777,6 +3952,11 @@
           <t>才</t>
         </is>
       </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%8D</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -2787,6 +3967,11 @@
           <t>结</t>
         </is>
       </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%93</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -2797,6 +3982,11 @@
           <t>反</t>
         </is>
       </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%8D</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -2807,6 +3997,11 @@
           <t>受</t>
         </is>
       </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%97</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -2817,6 +4012,11 @@
           <t>目</t>
         </is>
       </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9B%AE</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -2827,6 +4027,11 @@
           <t>太</t>
         </is>
       </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%AA</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -2837,6 +4042,11 @@
           <t>量</t>
         </is>
       </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%87%8F</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -2847,6 +4057,11 @@
           <t>再</t>
         </is>
       </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%8D</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -2857,6 +4072,11 @@
           <t>感</t>
         </is>
       </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%84%9F</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -2867,6 +4087,11 @@
           <t>建</t>
         </is>
       </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BB%BA</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -2877,6 +4102,11 @@
           <t>务</t>
         </is>
       </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%A1</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -2887,6 +4117,11 @@
           <t>做</t>
         </is>
       </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%81%9A</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -2897,6 +4132,11 @@
           <t>接</t>
         </is>
       </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8E%A5</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -2907,6 +4147,11 @@
           <t>必</t>
         </is>
       </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BF%85</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -2917,6 +4162,11 @@
           <t>场</t>
         </is>
       </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9C%BA</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -2925,6 +4175,11 @@
       <c r="B251" t="inlineStr">
         <is>
           <t>件</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%B6</t>
         </is>
       </c>
     </row>

--- a/hanzicraft_dashboard.xlsx
+++ b/hanzicraft_dashboard.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C251"/>
+  <dimension ref="A1:C501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4183,6 +4183,3756 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>计</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>管</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AE%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>期</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>市</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>直</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9B%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>德</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BE%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>资</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B5%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>命</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>山</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%87%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>指</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8C%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>克</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>许</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>统</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>区</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>保</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BF%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>至</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%87%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>队</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%98%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>形</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BD%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>社</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A4%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>便</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BE%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A9%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>决</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>治</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B2%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>展</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>马</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A9%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>科</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A7%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>司</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>基</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9F%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>眼</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9C%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>书</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>非</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9D%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>则</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>听</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%99%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>却</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>界</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%95%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>达</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>光</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>放</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%94%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>强</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>即</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>像</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%83%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>难</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9A%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>且</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>权</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9D%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>思</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%8E%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>象</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B1%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>完</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>设</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>式</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>色</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%89%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>路</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B7%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>记</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>南</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>品</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%93%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>住</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BD%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>告</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B1%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>求</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B1%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>据</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8D%AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>程</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A8%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>北</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>边</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>死</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AD%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>该</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>交</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>规</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>万</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>取</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>拉</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8B%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>格</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A0%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>望</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>觉</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>术</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>领</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A2%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>共</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>确</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A1%AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>传</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BC%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>师</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>观</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%82</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>清</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B8%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>切</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>院</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%99%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>让</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>识</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>候</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%80%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>带</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>导</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AF%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>争</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>运</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%90</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>笑</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AC%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>飞</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A3%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>风</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A3%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>步</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AD%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>改</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%94%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>收</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%94%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A0%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>干</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>造</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>言</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A8%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>联</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%81%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>持</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8C%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>组</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BB%84</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>每</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%AF%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>济</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>车</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BD%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>亲</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>极</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9E%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>林</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9E%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>服</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BF%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>办</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>议</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AE%AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>往</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BE%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>英</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8B%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>士</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A3%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>证</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>近</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%91</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>失</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>转</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BD%AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>夫</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>令</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>准</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>布</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B8%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>始</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A7%8B</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>怎</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%80%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>呢</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>存</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AD%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9C%AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>远</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>叫</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>台</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>单</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>影</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BD%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>具</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>罗</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BD%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>字</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AD%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>爱</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%88%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>击</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%87%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>流</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B5%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>备</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>兵</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>连</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BF%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>调</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B0%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>深</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B7%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>商</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%95%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AE%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>质</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>团</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9B%A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>集</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9B%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>百</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%99%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>需</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9C%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>价</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>花</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%8A%B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>党</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>华</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8D%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>城</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9F%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>石</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%9F%B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>级</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>整</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%95%B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>府</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BA%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>离</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A6%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>况</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>亚</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BA%9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>请</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>技</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%8A%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>际</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%99%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>约</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>示</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A4%BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>复</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A4%8D</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>病</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%97%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>息</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%81%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>究</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A9%B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>线</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%BA%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>似</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BC%BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>官</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%98</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%81%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>断</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%96%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>精</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%B2%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>满</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%BB%A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>支</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%94%AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>视</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A7%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>消</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B6%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>越</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B6%8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>器</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%99%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>容</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%AE%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>照</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%85%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>须</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A1%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>九</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>增</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A2%9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>研</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A0%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>写</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%99</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>称</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%A7%B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>企</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BC%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>八</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>功</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8A%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>吗</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%97</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>包</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>片</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%89%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>史</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>委</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%A7%94</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>乎</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B9%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>查</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9F%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>轻</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BD%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>易</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>早</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%97%A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>曾</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9B%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>除</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%99%A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>农</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%86%9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>找</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%89%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>装</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%A3%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>广</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B9%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>显</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%98%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>吧</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>阿</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%98%BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>李</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%9D%8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>标</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%A0%87</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>谈</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B0%88</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>吃</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%90%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>图</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%9B%BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>念</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BF%B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%85%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>引</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%BC%95</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>历</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8E%86</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>首</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%A6%96</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>医</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8C%BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>局</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B1%80</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>突</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E7%AA%81</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>专</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%B8%93</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>费</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%B4%B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>号</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>尽</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%B0%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>另</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%8F%A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>周</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%91%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>较</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%BE%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>注</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E6%B3%A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>语</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%AF%AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>仅</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E4%BB%85</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>考</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%80%83</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>落</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E8%90%BD</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9D%92</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>随</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%9A%8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>选</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E9%80%89</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>https://hanzicraft.com/dashboard/character/%E5%88%97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
